--- a/허브누리_레시피_목록_상세_p6of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p6of6_썸네일.xlsx
@@ -16314,7 +16314,15 @@
 칸데릴라왁스 사용시 밀랍 사용시</t>
         </is>
       </c>
-      <c r="H38" s="4" t="n"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법 (※ 이미지에 단계 캡션이 없어 공정 사진·레시피 기준으로 재구성)
+1. 호호바오일, 카렌듈라인퓨즈오일, 달맞이종자유, 동백오일, 시어버터, 칸데릴라왁스(밀랍)를 계량합니다.
+2. 핫플레이트/중탕으로 왁스가 녹을 때까지 데웁니다.
+3. 온도를 확인하고 적당히 식힌 뒤 라벤더·티트리·오렌지·저먼캐모마일 에센셜오일을 넣습니다.
+4. 잘 섞어 용기에 담아 굳히면 완성.</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="n"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -16785,7 +16793,7 @@
       <c r="I54" s="8" t="n"/>
       <c r="J54" s="8" t="n"/>
     </row>
-    <row r="55" ht="16" customHeight="1">
+    <row r="55" ht="16.5" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>아로마 물파스</t>
@@ -16820,7 +16828,18 @@
 ③ 올리브리퀴드 2g, 라벤더에센셜오일 10방울, 티트리에센셜오일 10방울, 로즈마리에센셜오일 20방울</t>
         </is>
       </c>
-      <c r="H55" s="4" t="n"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 알로에겔, 위치헤이즐워터, 하이셀을 계량한다.
+2. 스푼으로 저어가면서 데운다. 50도 정도 되면 걸쭉해진다.
+3. 멘톨을 비롯한 2번 재료를 넣는다.
+4. 골고루 저어준다.
+5~6. 3번 재료를 다른 용기에 계량한 후 골고루 섞어준다.
+7. 1+2번을 3번에 부어준다.
+8. 골고루 섞어준다.</t>
+        </is>
+      </c>
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -16828,7 +16847,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
+    <row r="56" ht="16.5" customHeight="1">
       <c r="C56" t="inlineStr">
         <is>
           <t>알로에겔(국내거제산)</t>
@@ -16845,7 +16864,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="16" customHeight="1">
+    <row r="57" ht="16.5" customHeight="1">
       <c r="C57" t="inlineStr">
         <is>
           <t>하이셀</t>
@@ -16862,7 +16881,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
+    <row r="58" ht="16.5" customHeight="1">
       <c r="C58" t="inlineStr">
         <is>
           <t>멘톨</t>
@@ -16879,7 +16898,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="16" customHeight="1">
+    <row r="59" ht="16.5" customHeight="1">
       <c r="C59" t="inlineStr">
         <is>
           <t>식물성에탄올</t>
@@ -16901,7 +16920,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1">
+    <row r="60" ht="16.5" customHeight="1">
       <c r="C60" t="inlineStr">
         <is>
           <t>인플라신</t>
@@ -16923,7 +16942,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
+    <row r="61" ht="16.5" customHeight="1">
       <c r="C61" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
@@ -16945,7 +16964,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="16" customHeight="1">
+    <row r="62" ht="16.5" customHeight="1">
       <c r="C62" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
@@ -16967,7 +16986,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
+    <row r="63" ht="16.5" customHeight="1">
       <c r="C63" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
@@ -16989,7 +17008,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="16" customHeight="1">
+    <row r="64" ht="16.5" customHeight="1">
       <c r="C64" t="inlineStr">
         <is>
           <t>로즈마리에센셜오일</t>
@@ -19614,7 +19633,7 @@
       <c r="I140" s="8" t="n"/>
       <c r="J140" s="8" t="n"/>
     </row>
-    <row r="141" ht="20" customHeight="1">
+    <row r="141" ht="30" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
           <t>로즈아로마스킨</t>
@@ -19650,7 +19669,17 @@
 원하는 다른 오일 8방울로 대체하셔도 되요.</t>
         </is>
       </c>
-      <c r="H141" s="4" t="n"/>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 용기 하나에 올리브리퀴드를 계량하고
+2. 기울여서 에센셜오일도 떨어뜨려 주세요.
+3. 스푼으로 잘 섞어주세요.
+4. 다른 용기는 워터를 미리 계량하세요.
+5~6. 워터를 올리브리퀴드와 에센셜오일 용기에 천천히 붓고 젓고, 붓고 저어주고 섞어주세요.
+7. 식물성글리세린과 플라센타를 넣어주세요. (보습을 더 원하신다면 글리세린양을 늘여주세요. 대체재료로 히아루론산은 유화가 분리·엉김현상이 생겨 권하지 않습니다.)</t>
+        </is>
+      </c>
       <c r="I141" s="4" t="n"/>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -19658,7 +19687,7 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="20" customHeight="1">
+    <row r="142" ht="30" customHeight="1">
       <c r="C142" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
@@ -19680,7 +19709,7 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="20" customHeight="1">
+    <row r="143" ht="30" customHeight="1">
       <c r="C143" t="inlineStr">
         <is>
           <t>로즈앱솔루트에센셜오일</t>
@@ -19702,7 +19731,7 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="20" customHeight="1">
+    <row r="144" ht="30" customHeight="1">
       <c r="C144" t="inlineStr">
         <is>
           <t>만다린에센셜오일</t>
@@ -19724,7 +19753,7 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="20" customHeight="1">
+    <row r="145" ht="30" customHeight="1">
       <c r="C145" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
@@ -19746,7 +19775,7 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="20" customHeight="1">
+    <row r="146" ht="30" customHeight="1">
       <c r="C146" t="inlineStr">
         <is>
           <t>식물성플라센타</t>

--- a/허브누리_레시피_목록_상세_p6of6_썸네일.xlsx
+++ b/허브누리_레시피_목록_상세_p6of6_썸네일.xlsx
@@ -914,7 +914,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -3089,7 +3089,7 @@
       <row>115</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="118" name="Image 118" descr="Picture"/>
